--- a/healthcare_forms/010_healthcare_provider_review_form--healthcare_forms.xlsx
+++ b/healthcare_forms/010_healthcare_provider_review_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'healthcare_forms'}</t>
+          <t>healthcare_forms</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Healthcare Forms'}</t>
+          <t>Healthcare Forms</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'other_form'}</t>
+          <t>other_form</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Other Form'}</t>
+          <t>Other Form</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'highly_likely'}</t>
+          <t>highly_likely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Highly Likely'}</t>
+          <t>Highly Likely</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely'}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Not Likely'}</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_likely'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Not at All Likely'}</t>
+          <t>Not at All Likely</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely'}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Not Likely'}</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_likely'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Not at All Likely'}</t>
+          <t>Not at All Likely</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
